--- a/fixtures/templates/测试用例模板.xlsx
+++ b/fixtures/templates/测试用例模板.xlsx
@@ -442,9 +442,9 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -510,17 +510,17 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>关联缺陷ID</t>
+          <t>回归测试标识</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>回归测试标识</t>
+          <t>知识库关联</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>知识库关联</t>
+          <t>质量评分</t>
         </is>
       </c>
     </row>
